--- a/tests/realSuite/Piano-Giocopallamano_3-marzo-26_con-vettore/input.xlsx
+++ b/tests/realSuite/Piano-Giocopallamano_3-marzo-26_con-vettore/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,315 +436,300 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IC ALTA VAL DI SOLE</t>
+          <t>IC BORGO VALSUGANA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ossana, Via S Michele, 11</t>
+          <t>Tezze di Grigno, Via Nazionale, 4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC BORGO VALSUGANA</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tezze di Grigno, Via Nazionale, 4</t>
+          <t>Pieve di Bono, Via Fiera, 1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC CHIESE</t>
+          <t>IC CIVEZZANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pieve di Bono, Via Fiera, 1</t>
+          <t>Albiano, Fermata Bus Chiesa</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC CIVEZZANO</t>
+          <t>IC CLES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Albiano, Fermata Bus Chiesa</t>
+          <t>Cles, Piazza Fiera</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC CLES</t>
+          <t>IC DRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cles, Piazza Fiera</t>
+          <t>Dro, Piazza Repubblica, 1</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC DRO</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dro, Piazza Repubblica, 1</t>
+          <t>Comano Terme, Fermata Bus Scuola Primaria Campo</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC GIUDICARIE ESTERIORI</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Comano Terme, Fermata Bus Scuola Primaria Campo</t>
+          <t>San Giovanni, Strada Dolomites, 6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC LADINO DI FASSA</t>
+          <t>IC LEVICO TERME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Giovanni, Strada Dolomites, 6</t>
+          <t>Caldonazzo, Via Guglielmo Marconi, 9</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC LEVICO TERME</t>
+          <t>IC MEZZANO SANTA CROCE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Caldonazzo, Via Guglielmo Marconi, 9</t>
+          <t>Mezzano, Via Molaren, 29</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC MEZZANO SANTA CROCE</t>
+          <t>IC MEZZOCORONA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mezzano, Via Molaren, 29</t>
+          <t>San Michele all’Adige, Via Biasi, 1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC MEZZOCORONA</t>
+          <t>IC MEZZOLOMBARDO-PAGANELLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>San Michele all’Adige, Via Biasi, 1</t>
+          <t>Spormaggiore, Via Alt Spaur, 5</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO-PAGANELLA</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spormaggiore, Via Alt Spaur, 5</t>
+          <t>Canezza, Fermata Trentino Trasporti</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC RIVA 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Canezza, Fermata Trentino Trasporti</t>
+          <t>Riva Del Garda, Viale Pernici, 21</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC RIVA 1</t>
+          <t>IC RIVA 2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Riva Del Garda, Viale Pernici, 21</t>
+          <t>Riva Del Garda, Viale Grez, 7</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC RIVA 2</t>
+          <t>IC STRIGNO TESINO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Riva Del Garda, Viale Grez, 7</t>
+          <t>Scurelle, Via XV Agosto, 68</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC STRIGNO TESINO</t>
+          <t>IC TAIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Scurelle, Via XV Agosto, 68</t>
+          <t>Taio, Piazza Della Chiesa</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Taio, Piazza Della Chiesa</t>
+          <t>Borgo Lares, Via Fucina, 10</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC TRENTO 6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Borgo Lares, Via Fucina, 10</t>
+          <t>Trento, Via Aldo Schmid, 4</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC TRENTO 6</t>
+          <t>IC TUENNO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Trento, Via Aldo Schmid, 4</t>
+          <t>Ville D’Anaunia, Via Maistrelli, 11</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC TUENNO</t>
+          <t>IC VEZZANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ville D’Anaunia, Via Maistrelli, 11</t>
+          <t>Vezzano, Via Roma, 3</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>IC VEZZANO</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Vezzano, Via Roma, 3</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
         <v>16</v>
       </c>
     </row>
